--- a/public/downloads/BS2018_cleantest.xlsx
+++ b/public/downloads/BS2018_cleantest.xlsx
@@ -747,13 +747,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="3">
-        <v>79.43262411347519</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="C3" s="3">
         <v>6.382978723404255</v>
       </c>
       <c r="D3" s="3">
-        <v>14.18439716312057</v>
+        <v>14.8936170212766</v>
       </c>
       <c r="E3" s="3">
         <v>1.418439716312057</v>
@@ -762,16 +762,16 @@
         <v>4.964539007092199</v>
       </c>
       <c r="G3" s="3">
-        <v>7.801418439716312</v>
+        <v>8.51063829787234</v>
       </c>
       <c r="H3" s="4">
-        <v>0.9327842847730599</v>
+        <v>0.8441984459695121</v>
       </c>
       <c r="I3" s="4">
-        <v>0.6044470056807592</v>
+        <v>0.4306100199356471</v>
       </c>
       <c r="J3" s="4">
-        <v>0.9635163356894502</v>
+        <v>0.889193458887245</v>
       </c>
       <c r="K3" s="4">
         <v>92.93602547401986</v>
@@ -1038,13 +1038,13 @@
         <v>17</v>
       </c>
       <c r="B3" s="5">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C3" s="5">
         <v>9</v>
       </c>
       <c r="D3" s="5">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5">
         <v>2</v>
@@ -1053,7 +1053,7 @@
         <v>7</v>
       </c>
       <c r="G3" s="5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" s="5">
         <v>2</v>
@@ -1236,16 +1236,16 @@
         <v>1</v>
       </c>
       <c r="N3" s="4">
-        <v>0.4819967375072111</v>
+        <v>0.267382858777637</v>
       </c>
       <c r="O3" s="5">
         <v>40</v>
       </c>
       <c r="P3" s="4">
-        <v>0.6625240943391528</v>
+        <v>0.6174521611651375</v>
       </c>
       <c r="Q3" s="4">
-        <v>0.4737078530445352</v>
+        <v>0.4303962350517255</v>
       </c>
       <c r="R3" s="5">
         <v>39</v>
@@ -1295,16 +1295,16 @@
         <v>7</v>
       </c>
       <c r="N4" s="4">
-        <v>0.7889149889933134</v>
+        <v>0.2390482973569306</v>
       </c>
       <c r="O4" s="5">
         <v>39</v>
       </c>
       <c r="P4" s="4">
-        <v>1.17576245827131</v>
+        <v>1.017583403337549</v>
       </c>
       <c r="Q4" s="4">
-        <v>0.6624570980941896</v>
+        <v>0.2754816041374966</v>
       </c>
       <c r="R4" s="5">
         <v>32</v>
@@ -1354,22 +1354,22 @@
         <v>7</v>
       </c>
       <c r="N5" s="4">
-        <v>0.8483230237058333</v>
+        <v>0.5083931279432363</v>
       </c>
       <c r="O5" s="5">
         <v>44</v>
       </c>
       <c r="P5" s="4">
-        <v>0.9600663017087172</v>
+        <v>0.8975597734058496</v>
       </c>
       <c r="Q5" s="4">
-        <v>0.6835324689876605</v>
+        <v>0.554921192835991</v>
       </c>
       <c r="R5" s="5">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="S5" s="5">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
